--- a/2022 data/excel_outputs/17_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/17_boothwise_data.xlsx
@@ -14,786 +14,1254 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="439">
   <si>
     <t>AC 17 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>####0##0 ###### ####</t>
-  </si>
-  <si>
-    <t>####0##0 #####</t>
-  </si>
-  <si>
-    <t>####0##0 #########</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ######## ##### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ######## ##### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ######## ##### ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ######## ##### ######## #### ##0 4</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ##### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ##### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ##### #### ##0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ####### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ####### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #### ########</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #### ##0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ######</t>
-  </si>
-  <si>
-    <t>######## ####### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ###</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ###### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ###### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ###### #### ##0 3</t>
-  </si>
-  <si>
-    <t>####0##0 #### ### ##### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 #### ### ##### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 #### ### #######</t>
-  </si>
-  <si>
-    <t>##### ##0##0 #### ###</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ##### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ##### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ##### #### ##0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ###</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #### ##0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ##0 3</t>
-  </si>
-  <si>
-    <t>#### #0##0 #######</t>
-  </si>
-  <si>
-    <t>####0##0 ##0###### ####### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##0###### ####### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### #### ####### ### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### #### ####### ### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### #### ####### ### #### ##0 3</t>
-  </si>
-  <si>
-    <t>######## ###### #### ##0 1</t>
-  </si>
-  <si>
-    <t>######## ###### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ###### ###</t>
-  </si>
-  <si>
-    <t>####0##0 #######</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ####### ### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ####### ### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ######</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ### #### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #####</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ####### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ####### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ### #### ##0 3</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ####### ###### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ####### ###### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ####</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ###### ###### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ###### ###### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ###### ###### #### ##0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ####</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ########</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##### ######## ####</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #####</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 #### ###</t>
-  </si>
-  <si>
-    <t>####0##0 #### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ##### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ##0###### #### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##0###### #### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##0###### #### #### ##0 3</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ######### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ######### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ######### #### ##0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ############ #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ############ #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ########</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ####### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ####### #### ##0 2</t>
-  </si>
-  <si>
-    <t>#### ####### #### ####### #### ##0 1</t>
-  </si>
-  <si>
-    <t>#### ####### #### ####### #### ##0 2</t>
-  </si>
-  <si>
-    <t>#### ### #### #0##0 ####### #### ##0 1</t>
-  </si>
-  <si>
-    <t>#### ### #### #0##0 ####### #### ##0 2</t>
-  </si>
-  <si>
-    <t>#### ### #### #0##0 ####### #### ##0 3</t>
-  </si>
-  <si>
-    <t>#### ### #### #0##0 ####### #### ##0 4</t>
-  </si>
-  <si>
-    <t>#### ### #### #0##0 ####### #### ##0 5</t>
-  </si>
-  <si>
-    <t>#### ### #### #0##0 ####### #### ##0 6</t>
-  </si>
-  <si>
-    <t>#### ### #### #0##0 ####### #### ##0 7</t>
-  </si>
-  <si>
-    <t>####### #### ##### ##0 ####### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####### #### ##### ##0 ####### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ########### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ########### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ##0#########</t>
-  </si>
-  <si>
-    <t>#### ####0##0 ########</t>
-  </si>
-  <si>
-    <t>#### ####0##0 ######## ### #### ##### #### ##0 1</t>
-  </si>
-  <si>
-    <t>#### ####0##0 ######## ### #### ##### #### ##0 2</t>
-  </si>
-  <si>
-    <t>#### ####0##0 ######## ### #### ##### #### ##0 3</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ######### #### ##0 4</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ##0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #######</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ######## ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ######## ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ######## ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ##0###### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #####</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ####### ##### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ####### ##### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #####</t>
-  </si>
-  <si>
-    <t>##0##0#0#0##0 ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>##0##0#0#0##0 ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0##0#0#0##0 ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>##0##0#0#0##0 ######## #### ##0 4</t>
-  </si>
-  <si>
-    <t>##0##0#0#0##0 ######## #### ##0 5</t>
-  </si>
-  <si>
-    <t>##0##0#0#0##0 ######## #### ##0 6</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ######## #### ##0 4</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ######## #### ##0 5</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ######## #### ##0 6</t>
-  </si>
-  <si>
-    <t>##0##0##0#0##0 ######## #### ##0 7</t>
-  </si>
-  <si>
-    <t>### ### ##### ########### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>### ### ##### ########### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>### ### ##### ########### ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>##0### #### ###### #0##0 ####### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>##0### #### ###### #0##0 ####### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0### #### ###### #0##0 ####### ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>##0### #### ###### #0##0 ####### ######## #### ##0 4</t>
-  </si>
-  <si>
-    <t>##0### #### ###### #0##0 ####### ######## #### ##0 5</t>
-  </si>
-  <si>
-    <t>##0### #### ###### #0##0 ####### ######## #### ##0 6</t>
-  </si>
-  <si>
-    <t>##0### #### ###### #0##0 ####### ######## #### ##0 7</t>
-  </si>
-  <si>
-    <t>##0#0##0 ######## ###### ### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##0#0##0 ######## ###### ### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0#0##0 ######## ###### ### #### ##0 3</t>
-  </si>
-  <si>
-    <t>##0#0##0 ######## ###### ### #### ##0 4</t>
-  </si>
-  <si>
-    <t>##0#0##0 ######## ### ### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##0#0##0 ######## ### ### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0#0##0 ######## ### ### #### ##0 3</t>
-  </si>
-  <si>
-    <t>##0#0##0 ######## ### ### #### ##0 4</t>
-  </si>
-  <si>
-    <t>##0#0##0 ######## ### ### #### ##0 5</t>
-  </si>
-  <si>
-    <t>##0#0##0 ######## ### ### #### ##0 6</t>
-  </si>
-  <si>
-    <t>##0#0##0 ######## ### ### #### ##0 7</t>
-  </si>
-  <si>
-    <t>##### ##0##### ##0 ##### ### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>##### ##0##### ##0 ##### ### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>##### #### ### ##### ##### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>##### #### ### ##### ##### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>##### #### ### ##### ##### ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>##0##0#### ### ###### ###### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>##0##0#### ### ###### ###### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0##0#### ### ###### ###### ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>##0##0#### ### ###### ###### ######## #### ##0 4</t>
-  </si>
-  <si>
-    <t>##0##0#### #0##0 ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>##0##0#### #0##0 ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0##0#### #0##0 ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>#### ##### ######## ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>#### ##### ######## ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>#### ### ##### ##### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>#### ### ##### ##### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>######### ##### ######### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>######### ##### ######### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>######### ##### ######### ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>######### ##### ######### ######## #### ##0 4</t>
-  </si>
-  <si>
-    <t>######### ##### ######### ######## #### ##0 5</t>
-  </si>
-  <si>
-    <t>##0##0##0 #0##0 ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 #0##0 ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 #0##0 ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>##0##0##0 #0##0 ######## #### ##0 4</t>
-  </si>
-  <si>
-    <t>##0##0##0 #0##0 ######## #### ##0 5</t>
-  </si>
-  <si>
-    <t>##0##0##0 #0##0 ######## #### ##0 6</t>
-  </si>
-  <si>
-    <t>##0##0##0 #0##0 ######## #### ##0 7</t>
-  </si>
-  <si>
-    <t>############ ###### #0##0 ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>############ ###### #0##0 ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>############ ###### #0##0 ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>############ ###### #0##0 ######## #### ##0 4</t>
-  </si>
-  <si>
-    <t>############ ###### #0##0 ######## #### ##0 5</t>
-  </si>
-  <si>
-    <t>############ ###### #0##0 ######## #### ##0 6</t>
-  </si>
-  <si>
-    <t>#### ####0##0 ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>#### ####0##0 ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>#### ####0##0 ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>####### #0##0 ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>####### #0##0 ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>####### #0##0 ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>####### #0##0 ######## #### ##0 4</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ##0 4</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ######## #### ##0 4</t>
-  </si>
-  <si>
-    <t>####0##0 ##########</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### #### ##0 2</t>
-  </si>
-  <si>
-    <t>#### ### ########### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>#### ### ########### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>#### ### ########### ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>##### ##### ##0##0 ######## #### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##### ##### ##0##0 ######## #### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##### ##### ##0##0 ######## #### #### ##0 3</t>
-  </si>
-  <si>
-    <t>##### ##### ##0##0 ######## #### #### ##0 4</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### #### ########## #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### #### ########## #### ##0 2</t>
-  </si>
-  <si>
-    <t>######### ##### ######## ### #### ##0 1</t>
-  </si>
-  <si>
-    <t>######### ##### ######## ### #### ##0 2</t>
-  </si>
-  <si>
-    <t>######### ##### ######## ### #### ##0 3</t>
-  </si>
-  <si>
-    <t>######### ##### ######## ### #### ##0 4</t>
-  </si>
-  <si>
-    <t>######### ##### ######## ### #### ##0 5</t>
-  </si>
-  <si>
-    <t>##### ##0 ##### ##0 ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>##### ##0 ##### ##0 ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>##### ######## ########</t>
-  </si>
-  <si>
-    <t>### ###### ######## ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>### ###### ######## ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>####### #### ##### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>####### #### ##### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>####### #### ##### ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>####### #### ##### ######## #### ##0 4</t>
-  </si>
-  <si>
-    <t>####0##0 ###########</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #########</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ###### #### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ###### #### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ###### #### #### ##0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ######## #### ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ######## #### ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ######## #### ######## #### ##0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ###### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ###### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ############</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ####</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ###### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##0 ### #### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ###</t>
-  </si>
-  <si>
-    <t>####0##0 ########### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ############ #####</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ######### ####</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ########## ###</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ########</t>
+    <t>PRA0VI0 RAMAPUR CHATHA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KAMAGARAPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KAMAGARAPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 (MUJAHIDA PATTI) BHAGUVALA KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 (MUJAHIDA PATTI) BHAGUVALA KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 (MUJAHIDA PATTI) BHAGUVALA KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 (MUJAHIDA PATTI) BHAGUVALA KAKSH NAM0-4</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BHAGUVALA PRATHAM KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BHAGUVALA PRATHAM KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BHAGUVALA PRATHAM KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BHAGUVALA PRATHAM KAKSH NAM0-4</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MIRJAPUR URPH PRITAMAG.DH</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHYAMIVALA KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHYAMIVALA KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAMADAS VALI KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAMADAS VALI KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SABALAG.DH</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KASHIRAMAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAYAPUR KHAS KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAYAPUR KHAS KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 DAHIRAPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 DAHIRAPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 AURAMGAPUR BASAMTA</t>
+  </si>
+  <si>
+    <t>PAMCHAYATAGHAR AURAMGAPUR BASAMTA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HASANAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PHARAJAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAPHIPUR MOHAN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KARAULI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MIRAMAPUR BEGA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MIRJAPUR SAID</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 JALAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SARAY ALAM PRATHAM KAKSH-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SARAY ALAM PRATHAM KAKSH-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SARAY ALAM DVITIY</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 SARAY ALAM</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 SHAHAJADAPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 SHAHAJADAPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 NAMGAL KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 NAMGAL KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 NAMGAL KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 NAMGAL KAKSH NAM0-4</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 JITAPUR KHAS</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HARACHANDAPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HARACHANDAPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SAUPHATAPUR PRATHAM</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SAUPHATAPUR DVITIY</t>
+  </si>
+  <si>
+    <t>PRA0VI0 TISOTARA KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 TISOTARA KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 TISOTARA KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>NUTAN IM0KA0 TISOTARA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MO0ALIPUR DVARAKA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PRRITHVIPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 LALAPUR SHAUJIMAL</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SUMGARAPUR KAKSH SAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SUMGARAPUR KAKSH SAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KAMARAJAPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KAMARAJAPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHANDOK KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHANDOK KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 DHARMAPUR BHOJA URPH PUNDARI KALAM KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 DHARMAPUR BHOJA URPH PUNDARI KALAM KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PAMCHAYATAGHAR BARAMAPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PAMCHAYATAGHAR BARAMAPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PUNDARI KHURD KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PUNDARI KHURD KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SABALAPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SABALAPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 LALAPUR MAN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BAKARAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAMANAGAR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SADULLAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHAMARAULA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RASULAPUR SAID KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RASULAPUR SAID KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHERAPUR ABHIA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HAREVALI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 DINAUDA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAHARAYAPUR SHEKH URPH DINAUDI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAGHUNATHAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAJAPUR NAVADA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SIKARAUDA KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SIKARAUDA KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 MANDAVALI KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 MANDAVALI KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 MANDAVALI KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SAIPHABAD</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NARAYANAPUR RATAN KAKSH SAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NARAYANAPUR RATAN KAKSH SAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NARAYANAPUR RATAN ATI0 KAKSH</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HAKUMATAPUR KESHO</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 JATAPURA BAUNDA KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 JATAPURA BAUNDA KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 JATAPURA BAUNDA KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 JATAPURA BAUNDA KAKSH NAM0-4</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GU.DHA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GULALAVALI</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 PREMAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAHAMAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAHATAPUR KHURD KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAHATAPUR KHURD KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAJARAMAPUR TULASI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MUSSEPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHEKHAPURA ALAM</t>
+  </si>
+  <si>
+    <t>PRA0VI0 LAHAK KALAM</t>
+  </si>
+  <si>
+    <t>PRA0VI0 LAHAK KHURD</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHAHABAPURA UMARAV SIMH</t>
+  </si>
+  <si>
+    <t>PRA0VI0 DHANASINI KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 DHANASINI KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NAMGALA HARADAS</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAU0 ALIPUR HRRIDAY KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAU0 ALIPUR HRRIDAY KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAU0 ALIPUR HRRIDAY KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KALHE.DI</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 MUBARAKAPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 MUBARAKAPUR KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NAMGALA UBHBHAN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KISHORAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NARAYANAPUR ICHCHA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HAKIMAPUR DISAUNDI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KHALILAPUR</t>
+  </si>
+  <si>
+    <t>PU0MA0K0VI0 PADARATHAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 AMANULLAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NAMGALA PITHAURA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 VIJAYAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GIRADAVA SAHANAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SAHANAPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SAHANAPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SAHANAPUR DVITIY KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SAHANAPUR DVITIY KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>MAKATAB SIRAJUL ULUM SAHANAPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>MAKATAB SIRAJUL ULUM SAHANAPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>RAJA CHARAT SIMH IMTAR KALEJ SAHANAPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>RAJA CHARAT SIMH IMTAR KALEJ SAHANAPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>RAJA CHARAT SIMH IMTAR KALEJ SAHANAPUR KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>RAJA CHARAT SIMH IMTAR KALEJ SAHANAPUR KAKSH NAM0-4</t>
+  </si>
+  <si>
+    <t>RAJA CHARAT SIMH IMTAR KALEJ SAHANAPUR KAKSH NAM0-5</t>
+  </si>
+  <si>
+    <t>PHARUKUL ULUM K0VI0 SAHANAPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PHARUKUL ULUM K0VI0 SAHANAPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KHAIRULLAPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 PURANAPUR G.DHI KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 PURANAPUR G.DHI KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAMAPUR MAMGAL</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BIJAURI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MANUPURA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MALUK VALI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BHOGAPUR</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 MAU0 AMIKHANAPUR</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 MEDUVALA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHATARUVALA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MOTADHAK</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KAUDI़YA</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 VIRUVALA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MATHURAPUR MOR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MATHURAPUR MOR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MATHURAPUR MOR KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 JASAVANTAPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 JASAVANTAPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 JASAVANTAPUR KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SAMIPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SAMIPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAHAVATAPUR BILLOCH</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 PARVATAPUR MAKHADUMAPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 PARVATAPUR MAKHADUMAPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ISSEPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ISSEPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 AJAMAPUR GAJI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAU0 ALIPUR PARAMA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BHADAULA</t>
+  </si>
+  <si>
+    <t>PRA0VI0SARAY SAID GHODA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 JHAKKAKI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAUJJAMAPUR SADAT</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAMPURI KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAMPURI KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 RAMPURI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KANAKAPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KANAKAPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 AKABARAPUR AMVALA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KISHANAPUR AMVALA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KISHANAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 JAHANABAD</t>
+  </si>
+  <si>
+    <t>PRA0VI0 AKABARAPUR CHAIGAMVA KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 AKABARAPUR CHAIGAMVA KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAUJJAMAPUR TULASI KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAUJJAMAPUR TULASI KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>MU0DE0K0I0 KALEJ NAJIBABAD KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>MU0DE0K0I0 KALEJ NAJIBABAD KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>MU0DE0K0I0 KALEJ NAJIBABAD KAKSH NAM0-4</t>
+  </si>
+  <si>
+    <t>MU0DE0K0I0 KALEJ NAJIBABAD KAKSH NAM0-5</t>
+  </si>
+  <si>
+    <t>MU0DE0K0I0 KALEJ NAJIBABAD KAKSH NAM0-6</t>
+  </si>
+  <si>
+    <t>EM0DI0ES0I0KA0 NAJIBABAD KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>EM0DI0ES0I0KA0 NAJIBABAD KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>EM0DI0ES0I0KA0 NAJIBABAD KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>RAMA JAIN KANYA MAHAVIDYALAY NAJIBABAD KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>RAMA JAIN KANYA MAHAVIDYALAY NAJIBABAD KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>MAU0 ALI JAUHAR GALRS I0KA0 RAMPURA NAJIBABAD KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>MAU0 ALI JAUHAR GALRS JU0HA0 SKUL RAMPURA NAJIBABAD KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>MAU0 ALI JAUHAR GALRS JU0HA0 SKUL RAMPURA NAJIBABAD KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>MAU0 ALI JAUHAR GALRS JU0HA0 SKUL RAMPURA NAJIBABAD KAKSH NAM0-4</t>
+  </si>
+  <si>
+    <t>MAU0 ALI JAUHAR GALRS JU0HA0 SKUL RAMPURA NAJIBABAD KAKSH NAM0-5</t>
+  </si>
+  <si>
+    <t>MAU0 ALI JAUHAR GALRS JU0HA0 SKUL RAMPURA NAJIBABAD KAKSH NAM0-6</t>
+  </si>
+  <si>
+    <t>MAU0 ALI JAUHAR GALRS JU0HA0 SKUL RAMPURA NAJIBABAD KAKSH NAM0-7</t>
+  </si>
+  <si>
+    <t>SAR SAIYAD MAIMA0JU0HA0SKUL, RAMPURA KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>SAR SAIYAD MAIMA0JU0HA0SKUL, RAMPURA KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>N0PA0PR0VI0 MUNNI DARI NAJIBABAD KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>N0PA0PR0VI0 MUNNI DARI NAJIBABAD KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>RA0I0KA0 NAJIBABAD PURANA BHAVAN KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>RA0I0KA0 NAJIBABAD PURANA BHAVAN KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>RA0I0KA0 NAJIBABAD PURANA BHAVAN KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>RA0I0KA0 NAJIBABAD PURANA BHAVAN KAKSH NAM0-4</t>
+  </si>
+  <si>
+    <t>RA0I0KA0 NAJIBABAD NAYA BHAVAN KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>RA0I0KA0 NAJIBABAD NAYA BHAVAN KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>RA0I0KA0 NAJIBABAD NAYA BHAVAN KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>RA0I0KA0 NAJIBABAD NAYA BHAVAN KAKSH NAM0-4</t>
+  </si>
+  <si>
+    <t>RA0I0KA0 NAJIBABAD NAYA BHAVAN KAKSH NAM0-5</t>
+  </si>
+  <si>
+    <t>RA0I0KA0 NAJIBABAD NAYA BHAVAN KAKSH NAM0-6</t>
+  </si>
+  <si>
+    <t>PURV MA0 KANYA VI0 VAHID NAGAR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PURV MA0 KANYA VI0 VAHID NAGAR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>HARANAM SIMH BAL VIHAR SKUL NAJIBABAD KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>HARANAM SIMH BAL VIHAR SKUL NAJIBABAD KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>AR0EN0KE0 BAL VIDYA MANIDAR NAJIBABAD KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>AR0EN0KE0 BAL VIDYA MANIDAR NAJIBABAD KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>AR0EN0KE0 BAL VIDYA MANIDAR NAJIBABAD KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>AR0EN0KE0 BAL VIDYA MANIDAR NAJIBABAD KAKSH NAM0-4</t>
+  </si>
+  <si>
+    <t>AR0EN0 KELA I0KA0 NAJIBABAD KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>AR0EN0 KELA I0KA0 NAJIBABAD KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>AR0EN0 KELA I0KA0 NAJIBABAD KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>KHAND VIKAS KARYALAY NAJIBABAD KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>KHAND VIKAS KARYALAY NAJIBABAD KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>KRRISHIA BHAVAN, TAHASIL PARISAR, NAJIBABAD KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>KRRISHIA BHAVAN, TAHASIL PARISAR, NAJIBABAD KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>ISLAMIYA SKUL JABTAGAMJ, NAJIBABAD KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>ISLAMIYA SKUL JABTAGAMJ, NAJIBABAD KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>ISLAMIYA SKUL JABTAGAMJ, NAJIBABAD KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>ISLAMIYA SKUL JABTAGAMJ, NAJIBABAD KAKSH NAM0-4</t>
+  </si>
+  <si>
+    <t>M0GAM0I0 KA0 NAJIBABAD KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>M0GAM0I0 KA0 NAJIBABAD KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>M0GAM0I0 KA0 NAJIBABAD KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>M0GAM0I0 KA0 NAJIBABAD KAKSH NAM0-4</t>
+  </si>
+  <si>
+    <t>M0GAM0I0 KA0 NAJIBABAD KAKSH NAM0-5</t>
+  </si>
+  <si>
+    <t>NAJIBUDDAULA GALRS I0KA0 NAJIBABAD KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>NAJIBUDDAULA GALRS I0KA0 NAJIBABAD KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>NAJIBUDDAULA GALRS I0KA0 NAJIBABAD KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>NAJIBUDDAULA GALRS I0KA0 NAJIBABAD KAKSH NAM0-4</t>
+  </si>
+  <si>
+    <t>NAJIBUDDAULA GALRS I0KA0 NAJIBABAD KAKSH NAM0-5</t>
+  </si>
+  <si>
+    <t>UCHCH PRA0VI0 NAJIBABAD KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>UCHCH PRA0VI0 NAJIBABAD KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>UCHCH PRA0VI0 NAJIBABAD KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>UCHCH PRA0VI0 NAJIBABAD KAKSH NAM0-4</t>
+  </si>
+  <si>
+    <t>KASAMIYA SKUL HARSHAVA.DA KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>KASAMIYA SKUL HARSHAVA.DA KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>KASAMIYA SKUL HARSHAVA.DA KAKSH NAM0-4</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ALIPURA KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ALIPURA KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ALIPURA KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 DARIYAPUR</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 DARIYAPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 DARIYAPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 DARIYAPUR KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 JALABAPUR GUD.D KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 JALABAPUR GUD.D KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHAHAJAHAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KHUSHAHALAPUR M.DAKA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 TATARAPUR LALU KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 TATARAPUR LALU KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>SAHU JAIN MAHAVIDYALAY NAJIBABAD KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>SAHU JAIN MAHAVIDYALAY NAJIBABAD KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>ABHIANAV PURV MA0VI0 TATARAPUR LALU KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>ABHIANAV PURV MA0VI0 TATARAPUR LALU KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>ABHIANAV PURV MA0VI0 TATARAPUR LALU KAKSH NAM0-4</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAHUKHEDI KAURA URPH RAJARAMAPUR</t>
+  </si>
+  <si>
+    <t>ISLAMIYA SKUL RAHUKHE.DI G.DHU KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>ISLAMIYA SKUL RAHUKHE.DI G.DHU KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>ISLAMIYA SKUL RAHUKHE.DI G.DHU KAKSH NAM0-3</t>
+  </si>
+  <si>
+    <t>PURV MADHYAMIK KANYA VIDYALAY JALALABAD KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PURV MADHYAMIK KANYA VIDYALAY JALALABAD KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>KANYA PATHASHALA JALALABAD</t>
+  </si>
+  <si>
+    <t>N0PAM0KA0 JALALABAD KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>N0PAM0KA0 JALALABAD KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>KASIMUL ULUM MADARASA JALALABAD KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>KASIMUL ULUM MADARASA JALALABAD KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>ISLAMIYA MADARASA JALALABAD KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>ISLAMIYA MADARASA JALALABAD KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 BAUREKI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NAJIMAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 DAUDAPUR NANHE.DA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BASHIRAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PURANAPUR NAROTTAM</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PHAJALAPUR KHAS KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PHAJALAPUR KHAS KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PRATAPAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAJARAMAPUR PHAJIL</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HIMAYUMPUR IDDU</t>
+  </si>
+  <si>
+    <t>PRA0VI0 JVALILALA KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 JVALILALA KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KUTUBAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 JVALACHANDI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PHAJALAPUR PHATEHAULLA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GAJIPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GAJIPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 PHAJALAPUR HABIB KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 PHAJALAPUR HABIB KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 AURAMGABAD URRPH HUSAINAPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 AURAMGABAD URRPH HUSAINAPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 AURAMGABAD URPH HUSAINAPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 AURAMGABAD URPH HUSAINAPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MOCHIPURA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHAHAPUR MIRA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 TAHARAPUR ISHHAK KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 TAHARAPUR ISHHAK KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MUSVIKHANAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HAKIMAPUR KAJI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BULACHANDAPUR</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 SHEKHAPUR LALA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KARAMASAKHE.DI</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 GAJARAULA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 AJAMAPUR MAU0 ALI URPH KHANAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MUSTAPHAPUR ASU</t>
+  </si>
+  <si>
+    <t>PRA0VI0 IBRAHIMAPUR BAVAN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PHATEHAULLAPUR DURG</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KAMALAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SADATAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PHAJALAPUR TABELA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 JAGADISHAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SARAVANAPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SARAVANAPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 MUBARAKAPUR RATHE</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MANOHAR VALA</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 SIKANDARAPUR BASI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SIKANDARAPUR BASI KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SIKANDARAPUR BASI KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BEGAMAPUR BHAUNAVALA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ALAVALAPUR NAINU</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BHATAULI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MURASHADAPUR KAKSH NAM0-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MURASHADAPUR KAKSH NAM0-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM NO. 340</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM NO. 341</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM NO. 342</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM NO. 343</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM NO. 344</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM NO. 345</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 346</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 347</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 348</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 349</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 350</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 351</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 352</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 353</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 354</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 355</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 356</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 357</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 358</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 359</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 360</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 361</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 362</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 363</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 364</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 365</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 366</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 367</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 368</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 369</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 370</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 371</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 372</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 373</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 374</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 375</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 376</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 377</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 378</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 379</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 380</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 381</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 382</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 383</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 384</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 385</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 386</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 387</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 388</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 389</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 390</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RANIKOTA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 391</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -869,8 +1337,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -886,7 +1362,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -894,12 +1370,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1198,85 +1692,157 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>260</v>
+        <v>416</v>
       </c>
       <c r="D2" t="s">
-        <v>261</v>
+        <v>417</v>
       </c>
       <c r="E2" t="s">
-        <v>262</v>
+        <v>418</v>
       </c>
       <c r="F2" t="s">
-        <v>263</v>
+        <v>419</v>
       </c>
       <c r="G2" t="s">
-        <v>264</v>
+        <v>420</v>
       </c>
       <c r="H2" t="s">
-        <v>265</v>
+        <v>421</v>
       </c>
       <c r="I2" t="s">
-        <v>266</v>
+        <v>422</v>
       </c>
       <c r="J2" t="s">
-        <v>267</v>
+        <v>423</v>
       </c>
       <c r="K2" t="s">
-        <v>268</v>
+        <v>424</v>
       </c>
       <c r="L2" t="s">
-        <v>269</v>
+        <v>425</v>
       </c>
       <c r="M2" t="s">
-        <v>270</v>
+        <v>426</v>
       </c>
       <c r="N2" t="s">
-        <v>271</v>
+        <v>427</v>
       </c>
       <c r="O2" t="s">
-        <v>272</v>
+        <v>428</v>
       </c>
       <c r="P2" t="s">
-        <v>273</v>
+        <v>429</v>
       </c>
       <c r="Q2" t="s">
-        <v>274</v>
+        <v>430</v>
       </c>
       <c r="R2" t="s">
-        <v>275</v>
+        <v>431</v>
       </c>
       <c r="S2" t="s">
-        <v>276</v>
+        <v>432</v>
       </c>
       <c r="T2" t="s">
-        <v>277</v>
+        <v>433</v>
       </c>
       <c r="U2" t="s">
-        <v>278</v>
+        <v>434</v>
       </c>
       <c r="V2" t="s">
-        <v>279</v>
+        <v>435</v>
       </c>
       <c r="W2" t="s">
-        <v>280</v>
+        <v>436</v>
       </c>
       <c r="X2" t="s">
-        <v>281</v>
+        <v>437</v>
       </c>
       <c r="Y2" t="s">
-        <v>282</v>
+        <v>438</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1284,7 +1850,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C3">
         <v>594</v>
@@ -1361,7 +1927,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C4">
         <v>1076</v>
@@ -1438,7 +2004,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C5">
         <v>769</v>
@@ -1515,7 +2081,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C6">
         <v>987</v>
@@ -1592,7 +2158,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>1127</v>
@@ -1669,7 +2235,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>1158</v>
@@ -1746,7 +2312,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>931</v>
@@ -1823,7 +2389,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C10">
         <v>1155</v>
@@ -1900,7 +2466,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C11">
         <v>1146</v>
@@ -1977,7 +2543,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C12">
         <v>1130</v>
@@ -2054,7 +2620,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C13">
         <v>757</v>
@@ -2131,7 +2697,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C14">
         <v>657</v>
@@ -2208,7 +2774,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C15">
         <v>525</v>
@@ -2285,7 +2851,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C16">
         <v>894</v>
@@ -2362,7 +2928,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="C17">
         <v>988</v>
@@ -2439,7 +3005,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C18">
         <v>1038</v>
@@ -2516,7 +3082,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="C19">
         <v>962</v>
@@ -2593,7 +3159,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="C20">
         <v>739</v>
@@ -2670,7 +3236,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C21">
         <v>795</v>
@@ -2747,7 +3313,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="C22">
         <v>769</v>
@@ -2824,7 +3390,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="C23">
         <v>653</v>
@@ -2901,7 +3467,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C24">
         <v>693</v>
@@ -2978,7 +3544,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="C25">
         <v>1042</v>
@@ -3055,7 +3621,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="C26">
         <v>844</v>
@@ -3132,7 +3698,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="C27">
         <v>1043</v>
@@ -3209,7 +3775,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C28">
         <v>1008</v>
@@ -3286,7 +3852,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="C29">
         <v>1094</v>
@@ -3363,7 +3929,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="C30">
         <v>964</v>
@@ -3440,7 +4006,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="C31">
         <v>805</v>
@@ -3517,7 +4083,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="C32">
         <v>787</v>
@@ -3594,7 +4160,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="C33">
         <v>641</v>
@@ -3671,7 +4237,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="C34">
         <v>984</v>
@@ -3748,7 +4314,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="C35">
         <v>1127</v>
@@ -3825,7 +4391,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="C36">
         <v>844</v>
@@ -3902,7 +4468,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="C37">
         <v>1112</v>
@@ -3979,7 +4545,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="C38">
         <v>1154</v>
@@ -4056,7 +4622,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="C39">
         <v>767</v>
@@ -4133,7 +4699,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="C40">
         <v>801</v>
@@ -4210,7 +4776,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="C41">
         <v>766</v>
@@ -4287,7 +4853,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="C42">
         <v>1102</v>
@@ -4364,7 +4930,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="C43">
         <v>1082</v>
@@ -4441,7 +5007,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="C44">
         <v>825</v>
@@ -4518,7 +5084,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C45">
         <v>845</v>
@@ -4595,7 +5161,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="C46">
         <v>877</v>
@@ -4672,7 +5238,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="C47">
         <v>923</v>
@@ -4749,7 +5315,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="C48">
         <v>1047</v>
@@ -4826,7 +5392,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="C49">
         <v>1035</v>
@@ -4903,7 +5469,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C50">
         <v>893</v>
@@ -4980,7 +5546,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="C51">
         <v>1095</v>
@@ -5057,7 +5623,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="C52">
         <v>722</v>
@@ -5134,7 +5700,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="C53">
         <v>1142</v>
@@ -5211,7 +5777,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="C54">
         <v>1082</v>
@@ -5288,7 +5854,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="C55">
         <v>677</v>
@@ -5365,7 +5931,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="C56">
         <v>726</v>
@@ -5442,7 +6008,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="C57">
         <v>741</v>
@@ -5519,7 +6085,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="C58">
         <v>704</v>
@@ -5596,7 +6162,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="C59">
         <v>600</v>
@@ -5673,7 +6239,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="C60">
         <v>998</v>
@@ -5750,7 +6316,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="C61">
         <v>913</v>
@@ -5827,7 +6393,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="C62">
         <v>973</v>
@@ -5904,7 +6470,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="C63">
         <v>951</v>
@@ -5981,7 +6547,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="C64">
         <v>766</v>
@@ -6058,7 +6624,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="C65">
         <v>745</v>
@@ -6135,7 +6701,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="C66">
         <v>625</v>
@@ -6212,7 +6778,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="C67">
         <v>654</v>
@@ -6289,7 +6855,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="C68">
         <v>954</v>
@@ -6366,7 +6932,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="C69">
         <v>877</v>
@@ -6443,7 +7009,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="C70">
         <v>744</v>
@@ -6520,7 +7086,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="C71">
         <v>789</v>
@@ -6597,7 +7163,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="C72">
         <v>796</v>
@@ -6674,7 +7240,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="C73">
         <v>778</v>
@@ -6751,7 +7317,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="C74">
         <v>1005</v>
@@ -6828,7 +7394,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="C75">
         <v>1064</v>
@@ -6905,7 +7471,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="C76">
         <v>796</v>
@@ -6982,7 +7548,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="C77">
         <v>821</v>
@@ -7059,7 +7625,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C78">
         <v>983</v>
@@ -7136,7 +7702,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="C79">
         <v>1044</v>
@@ -7213,7 +7779,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="C80">
         <v>1155</v>
@@ -7290,7 +7856,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="C81">
         <v>1149</v>
@@ -7367,7 +7933,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="C82">
         <v>772</v>
@@ -7444,7 +8010,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="C83">
         <v>1028</v>
@@ -7521,7 +8087,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>28</v>
+        <v>107</v>
       </c>
       <c r="C84">
         <v>861</v>
@@ -7598,7 +8164,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
       <c r="C85">
         <v>1134</v>
@@ -7675,7 +8241,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="C86">
         <v>738</v>
@@ -7752,7 +8318,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>29</v>
+        <v>110</v>
       </c>
       <c r="C87">
         <v>799</v>
@@ -7829,7 +8395,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>29</v>
+        <v>111</v>
       </c>
       <c r="C88">
         <v>383</v>
@@ -7906,7 +8472,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="C89">
         <v>1151</v>
@@ -7983,7 +8549,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="C90">
         <v>1168</v>
@@ -8060,7 +8626,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>45</v>
+        <v>114</v>
       </c>
       <c r="C91">
         <v>884</v>
@@ -8137,7 +8703,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>29</v>
+        <v>115</v>
       </c>
       <c r="C92">
         <v>989</v>
@@ -8214,7 +8780,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>66</v>
+        <v>116</v>
       </c>
       <c r="C93">
         <v>833</v>
@@ -8291,7 +8857,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="C94">
         <v>738</v>
@@ -8368,7 +8934,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>5</v>
+        <v>118</v>
       </c>
       <c r="C95">
         <v>746</v>
@@ -8445,7 +9011,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="C96">
         <v>1176</v>
@@ -8522,7 +9088,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="C97">
         <v>933</v>
@@ -8599,7 +9165,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="C98">
         <v>702</v>
@@ -8676,7 +9242,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="C99">
         <v>870</v>
@@ -8753,7 +9319,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="C100">
         <v>1070</v>
@@ -8830,7 +9396,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="C101">
         <v>773</v>
@@ -8907,7 +9473,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>41</v>
+        <v>125</v>
       </c>
       <c r="C102">
         <v>549</v>
@@ -8984,7 +9550,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="C103">
         <v>645</v>
@@ -9061,7 +9627,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="C104">
         <v>714</v>
@@ -9138,7 +9704,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="C105">
         <v>994</v>
@@ -9215,7 +9781,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="C106">
         <v>1013</v>
@@ -9292,7 +9858,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="C107">
         <v>895</v>
@@ -9369,7 +9935,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="C108">
         <v>1119</v>
@@ -9446,7 +10012,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="C109">
         <v>781</v>
@@ -9523,7 +10089,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="C110">
         <v>784</v>
@@ -9600,7 +10166,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="C111">
         <v>1138</v>
@@ -9677,7 +10243,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="C112">
         <v>728</v>
@@ -9754,7 +10320,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="C113">
         <v>1073</v>
@@ -9831,7 +10397,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>5</v>
+        <v>137</v>
       </c>
       <c r="C114">
         <v>1007</v>
@@ -9908,7 +10474,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="C115">
         <v>1120</v>
@@ -9985,7 +10551,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>63</v>
+        <v>139</v>
       </c>
       <c r="C116">
         <v>376</v>
@@ -10062,7 +10628,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="C117">
         <v>1117</v>
@@ -10139,7 +10705,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>50</v>
+        <v>141</v>
       </c>
       <c r="C118">
         <v>692</v>
@@ -10216,7 +10782,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="C119">
         <v>795</v>
@@ -10293,7 +10859,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="C120">
         <v>685</v>
@@ -10370,7 +10936,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>5</v>
+        <v>144</v>
       </c>
       <c r="C121">
         <v>1041</v>
@@ -10447,7 +11013,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>86</v>
+        <v>145</v>
       </c>
       <c r="C122">
         <v>1042</v>
@@ -10524,7 +11090,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>87</v>
+        <v>146</v>
       </c>
       <c r="C123">
         <v>461</v>
@@ -10601,7 +11167,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="C124">
         <v>1142</v>
@@ -10678,7 +11244,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="C125">
         <v>466</v>
@@ -10755,7 +11321,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>90</v>
+        <v>149</v>
       </c>
       <c r="C126">
         <v>860</v>
@@ -10832,7 +11398,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="C127">
         <v>874</v>
@@ -10909,7 +11475,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>28</v>
+        <v>151</v>
       </c>
       <c r="C128">
         <v>1126</v>
@@ -10986,7 +11552,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>91</v>
+        <v>152</v>
       </c>
       <c r="C129">
         <v>785</v>
@@ -11063,7 +11629,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>92</v>
+        <v>153</v>
       </c>
       <c r="C130">
         <v>855</v>
@@ -11140,7 +11706,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>93</v>
+        <v>154</v>
       </c>
       <c r="C131">
         <v>870</v>
@@ -11217,7 +11783,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>94</v>
+        <v>155</v>
       </c>
       <c r="C132">
         <v>1115</v>
@@ -11294,7 +11860,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>63</v>
+        <v>156</v>
       </c>
       <c r="C133">
         <v>964</v>
@@ -11371,7 +11937,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="C134">
         <v>715</v>
@@ -11448,7 +12014,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="C135">
         <v>882</v>
@@ -11525,7 +12091,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="C136">
         <v>936</v>
@@ -11602,7 +12168,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>91</v>
+        <v>160</v>
       </c>
       <c r="C137">
         <v>743</v>
@@ -11679,7 +12245,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>40</v>
+        <v>161</v>
       </c>
       <c r="C138">
         <v>594</v>
@@ -11756,7 +12322,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>41</v>
+        <v>162</v>
       </c>
       <c r="C139">
         <v>773</v>
@@ -11833,7 +12399,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>63</v>
+        <v>163</v>
       </c>
       <c r="C140">
         <v>1012</v>
@@ -11910,7 +12476,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>98</v>
+        <v>164</v>
       </c>
       <c r="C141">
         <v>697</v>
@@ -11987,7 +12553,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>99</v>
+        <v>165</v>
       </c>
       <c r="C142">
         <v>649</v>
@@ -12064,7 +12630,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>100</v>
+        <v>165</v>
       </c>
       <c r="C143">
         <v>522</v>
@@ -12141,7 +12707,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>63</v>
+        <v>166</v>
       </c>
       <c r="C144">
         <v>844</v>
@@ -12218,7 +12784,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>51</v>
+        <v>167</v>
       </c>
       <c r="C145">
         <v>574</v>
@@ -12295,7 +12861,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>23</v>
+        <v>168</v>
       </c>
       <c r="C146">
         <v>648</v>
@@ -12372,7 +12938,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>24</v>
+        <v>169</v>
       </c>
       <c r="C147">
         <v>816</v>
@@ -12449,7 +13015,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>101</v>
+        <v>170</v>
       </c>
       <c r="C148">
         <v>1224</v>
@@ -12526,7 +13092,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>102</v>
+        <v>171</v>
       </c>
       <c r="C149">
         <v>544</v>
@@ -12603,7 +13169,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>103</v>
+        <v>172</v>
       </c>
       <c r="C150">
         <v>1043</v>
@@ -12680,7 +13246,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>104</v>
+        <v>173</v>
       </c>
       <c r="C151">
         <v>954</v>
@@ -12757,7 +13323,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>105</v>
+        <v>174</v>
       </c>
       <c r="C152">
         <v>1138</v>
@@ -12834,7 +13400,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>106</v>
+        <v>175</v>
       </c>
       <c r="C153">
         <v>1158</v>
@@ -12911,7 +13477,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>107</v>
+        <v>176</v>
       </c>
       <c r="C154">
         <v>741</v>
@@ -12988,7 +13554,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>108</v>
+        <v>177</v>
       </c>
       <c r="C155">
         <v>787</v>
@@ -13065,7 +13631,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>109</v>
+        <v>178</v>
       </c>
       <c r="C156">
         <v>931</v>
@@ -13142,7 +13708,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>110</v>
+        <v>179</v>
       </c>
       <c r="C157">
         <v>650</v>
@@ -13219,7 +13785,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
       <c r="C158">
         <v>1115</v>
@@ -13296,7 +13862,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>112</v>
+        <v>181</v>
       </c>
       <c r="C159">
         <v>978</v>
@@ -13373,7 +13939,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>113</v>
+        <v>182</v>
       </c>
       <c r="C160">
         <v>1108</v>
@@ -13450,7 +14016,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="C161">
         <v>1112</v>
@@ -13527,7 +14093,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
       <c r="C162">
         <v>1149</v>
@@ -13604,7 +14170,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>64</v>
+        <v>185</v>
       </c>
       <c r="C163">
         <v>1084</v>
@@ -13681,7 +14247,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>65</v>
+        <v>186</v>
       </c>
       <c r="C164">
         <v>1169</v>
@@ -13758,7 +14324,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>63</v>
+        <v>187</v>
       </c>
       <c r="C165">
         <v>952</v>
@@ -13835,7 +14401,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>3</v>
+        <v>188</v>
       </c>
       <c r="C166">
         <v>632</v>
@@ -13912,7 +14478,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>29</v>
+        <v>189</v>
       </c>
       <c r="C167">
         <v>935</v>
@@ -13989,7 +14555,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>63</v>
+        <v>190</v>
       </c>
       <c r="C168">
         <v>666</v>
@@ -14066,7 +14632,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>100</v>
+        <v>191</v>
       </c>
       <c r="C169">
         <v>616</v>
@@ -14143,7 +14709,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>29</v>
+        <v>192</v>
       </c>
       <c r="C170">
         <v>1188</v>
@@ -14220,7 +14786,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>116</v>
+        <v>193</v>
       </c>
       <c r="C171">
         <v>874</v>
@@ -14297,7 +14863,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>83</v>
+        <v>194</v>
       </c>
       <c r="C172">
         <v>432</v>
@@ -14374,7 +14940,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>100</v>
+        <v>195</v>
       </c>
       <c r="C173">
         <v>149</v>
@@ -14451,7 +15017,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>63</v>
+        <v>196</v>
       </c>
       <c r="C174">
         <v>539</v>
@@ -14528,7 +15094,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>29</v>
+        <v>197</v>
       </c>
       <c r="C175">
         <v>435</v>
@@ -14605,7 +15171,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>117</v>
+        <v>198</v>
       </c>
       <c r="C176">
         <v>1099</v>
@@ -14682,7 +15248,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>118</v>
+        <v>199</v>
       </c>
       <c r="C177">
         <v>803</v>
@@ -14759,7 +15325,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>119</v>
+        <v>200</v>
       </c>
       <c r="C178">
         <v>980</v>
@@ -14836,7 +15402,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>120</v>
+        <v>201</v>
       </c>
       <c r="C179">
         <v>803</v>
@@ -14913,7 +15479,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>95</v>
+        <v>202</v>
       </c>
       <c r="C180">
         <v>1060</v>
@@ -14990,7 +15556,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>96</v>
+        <v>203</v>
       </c>
       <c r="C181">
         <v>1047</v>
@@ -15067,7 +15633,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>97</v>
+        <v>204</v>
       </c>
       <c r="C182">
         <v>1021</v>
@@ -15144,7 +15710,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>121</v>
+        <v>205</v>
       </c>
       <c r="C183">
         <v>1020</v>
@@ -15221,7 +15787,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>27</v>
+        <v>206</v>
       </c>
       <c r="C184">
         <v>1090</v>
@@ -15298,7 +15864,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>28</v>
+        <v>207</v>
       </c>
       <c r="C185">
         <v>926</v>
@@ -15375,7 +15941,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="C186">
         <v>1187</v>
@@ -15452,7 +16018,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>123</v>
+        <v>209</v>
       </c>
       <c r="C187">
         <v>922</v>
@@ -15529,7 +16095,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>124</v>
+        <v>210</v>
       </c>
       <c r="C188">
         <v>697</v>
@@ -15606,7 +16172,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>125</v>
+        <v>211</v>
       </c>
       <c r="C189">
         <v>581</v>
@@ -15683,7 +16249,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="C190">
         <v>993</v>
@@ -15760,7 +16326,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>40</v>
+        <v>213</v>
       </c>
       <c r="C191">
         <v>1054</v>
@@ -15837,7 +16403,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>41</v>
+        <v>214</v>
       </c>
       <c r="C192">
         <v>874</v>
@@ -15914,7 +16480,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>3</v>
+        <v>215</v>
       </c>
       <c r="C193">
         <v>1136</v>
@@ -15991,7 +16557,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>127</v>
+        <v>216</v>
       </c>
       <c r="C194">
         <v>1029</v>
@@ -16068,7 +16634,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>4</v>
+        <v>217</v>
       </c>
       <c r="C195">
         <v>1106</v>
@@ -16145,7 +16711,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>23</v>
+        <v>218</v>
       </c>
       <c r="C196">
         <v>714</v>
@@ -16222,7 +16788,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>24</v>
+        <v>219</v>
       </c>
       <c r="C197">
         <v>709</v>
@@ -16299,7 +16865,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="C198">
         <v>1154</v>
@@ -16376,7 +16942,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>27</v>
+        <v>221</v>
       </c>
       <c r="C199">
         <v>709</v>
@@ -16453,7 +17019,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>28</v>
+        <v>222</v>
       </c>
       <c r="C200">
         <v>752</v>
@@ -16530,7 +17096,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>33</v>
+        <v>223</v>
       </c>
       <c r="C201">
         <v>1171</v>
@@ -16607,7 +17173,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>34</v>
+        <v>224</v>
       </c>
       <c r="C202">
         <v>862</v>
@@ -16684,7 +17250,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>27</v>
+        <v>225</v>
       </c>
       <c r="C203">
         <v>918</v>
@@ -16761,7 +17327,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>28</v>
+        <v>226</v>
       </c>
       <c r="C204">
         <v>906</v>
@@ -16838,7 +17404,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>66</v>
+        <v>227</v>
       </c>
       <c r="C205">
         <v>793</v>
@@ -16915,7 +17481,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>129</v>
+        <v>228</v>
       </c>
       <c r="C206">
         <v>818</v>
@@ -16992,7 +17558,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>130</v>
+        <v>229</v>
       </c>
       <c r="C207">
         <v>778</v>
@@ -17069,7 +17635,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>131</v>
+        <v>230</v>
       </c>
       <c r="C208">
         <v>757</v>
@@ -17146,7 +17712,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>63</v>
+        <v>231</v>
       </c>
       <c r="C209">
         <v>992</v>
@@ -17223,7 +17789,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>71</v>
+        <v>232</v>
       </c>
       <c r="C210">
         <v>634</v>
@@ -17300,7 +17866,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>72</v>
+        <v>233</v>
       </c>
       <c r="C211">
         <v>626</v>
@@ -17377,7 +17943,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>101</v>
+        <v>234</v>
       </c>
       <c r="C212">
         <v>1067</v>
@@ -17454,7 +18020,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>102</v>
+        <v>235</v>
       </c>
       <c r="C213">
         <v>960</v>
@@ -17531,7 +18097,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>49</v>
+        <v>236</v>
       </c>
       <c r="C214">
         <v>1151</v>
@@ -17608,7 +18174,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>50</v>
+        <v>237</v>
       </c>
       <c r="C215">
         <v>1084</v>
@@ -17685,7 +18251,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>132</v>
+        <v>238</v>
       </c>
       <c r="C216">
         <v>455</v>
@@ -17762,7 +18328,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>133</v>
+        <v>239</v>
       </c>
       <c r="C217">
         <v>703</v>
@@ -17839,7 +18405,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>134</v>
+        <v>240</v>
       </c>
       <c r="C218">
         <v>927</v>
@@ -17916,7 +18482,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>135</v>
+        <v>241</v>
       </c>
       <c r="C219">
         <v>920</v>
@@ -17993,7 +18559,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>136</v>
+        <v>242</v>
       </c>
       <c r="C220">
         <v>1032</v>
@@ -18070,7 +18636,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>137</v>
+        <v>243</v>
       </c>
       <c r="C221">
         <v>781</v>
@@ -18147,7 +18713,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>138</v>
+        <v>244</v>
       </c>
       <c r="C222">
         <v>554</v>
@@ -18224,7 +18790,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>139</v>
+        <v>245</v>
       </c>
       <c r="C223">
         <v>657</v>
@@ -18301,7 +18867,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>140</v>
+        <v>246</v>
       </c>
       <c r="C224">
         <v>661</v>
@@ -18378,7 +18944,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>141</v>
+        <v>247</v>
       </c>
       <c r="C225">
         <v>922</v>
@@ -18455,7 +19021,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>142</v>
+        <v>248</v>
       </c>
       <c r="C226">
         <v>472</v>
@@ -18532,7 +19098,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>143</v>
+        <v>249</v>
       </c>
       <c r="C227">
         <v>1069</v>
@@ -18609,7 +19175,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>144</v>
+        <v>250</v>
       </c>
       <c r="C228">
         <v>906</v>
@@ -18686,7 +19252,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>145</v>
+        <v>251</v>
       </c>
       <c r="C229">
         <v>868</v>
@@ -18763,7 +19329,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>146</v>
+        <v>252</v>
       </c>
       <c r="C230">
         <v>736</v>
@@ -18840,7 +19406,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>147</v>
+        <v>253</v>
       </c>
       <c r="C231">
         <v>1164</v>
@@ -18917,7 +19483,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>148</v>
+        <v>254</v>
       </c>
       <c r="C232">
         <v>914</v>
@@ -18994,7 +19560,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>149</v>
+        <v>255</v>
       </c>
       <c r="C233">
         <v>1001</v>
@@ -19071,7 +19637,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>150</v>
+        <v>256</v>
       </c>
       <c r="C234">
         <v>949</v>
@@ -19148,7 +19714,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>151</v>
+        <v>257</v>
       </c>
       <c r="C235">
         <v>1052</v>
@@ -19225,7 +19791,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>152</v>
+        <v>258</v>
       </c>
       <c r="C236">
         <v>732</v>
@@ -19302,7 +19868,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="C237">
         <v>849</v>
@@ -19379,7 +19945,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>154</v>
+        <v>260</v>
       </c>
       <c r="C238">
         <v>1072</v>
@@ -19456,7 +20022,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="C239">
         <v>742</v>
@@ -19533,7 +20099,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>156</v>
+        <v>262</v>
       </c>
       <c r="C240">
         <v>929</v>
@@ -19610,7 +20176,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>157</v>
+        <v>263</v>
       </c>
       <c r="C241">
         <v>1171</v>
@@ -19687,7 +20253,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>158</v>
+        <v>264</v>
       </c>
       <c r="C242">
         <v>1114</v>
@@ -19764,7 +20330,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="C243">
         <v>1045</v>
@@ -19841,7 +20407,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="C244">
         <v>1085</v>
@@ -19918,7 +20484,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>161</v>
+        <v>267</v>
       </c>
       <c r="C245">
         <v>737</v>
@@ -19995,7 +20561,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>162</v>
+        <v>268</v>
       </c>
       <c r="C246">
         <v>695</v>
@@ -20072,7 +20638,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="C247">
         <v>1191</v>
@@ -20149,7 +20715,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="C248">
         <v>913</v>
@@ -20226,7 +20792,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="C249">
         <v>807</v>
@@ -20303,7 +20869,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>166</v>
+        <v>272</v>
       </c>
       <c r="C250">
         <v>891</v>
@@ -20380,7 +20946,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="C251">
         <v>962</v>
@@ -20457,7 +21023,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="C252">
         <v>662</v>
@@ -20534,7 +21100,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>169</v>
+        <v>275</v>
       </c>
       <c r="C253">
         <v>901</v>
@@ -20611,7 +21177,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>170</v>
+        <v>276</v>
       </c>
       <c r="C254">
         <v>858</v>
@@ -20688,7 +21254,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>171</v>
+        <v>277</v>
       </c>
       <c r="C255">
         <v>1045</v>
@@ -20765,7 +21331,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>172</v>
+        <v>278</v>
       </c>
       <c r="C256">
         <v>1140</v>
@@ -20842,7 +21408,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="C257">
         <v>1235</v>
@@ -20919,7 +21485,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>174</v>
+        <v>280</v>
       </c>
       <c r="C258">
         <v>1117</v>
@@ -20996,7 +21562,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>175</v>
+        <v>281</v>
       </c>
       <c r="C259">
         <v>1157</v>
@@ -21073,7 +21639,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>176</v>
+        <v>282</v>
       </c>
       <c r="C260">
         <v>1094</v>
@@ -21150,7 +21716,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>177</v>
+        <v>283</v>
       </c>
       <c r="C261">
         <v>1185</v>
@@ -21227,7 +21793,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>178</v>
+        <v>284</v>
       </c>
       <c r="C262">
         <v>969</v>
@@ -21304,7 +21870,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>179</v>
+        <v>285</v>
       </c>
       <c r="C263">
         <v>981</v>
@@ -21381,7 +21947,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>180</v>
+        <v>286</v>
       </c>
       <c r="C264">
         <v>1066</v>
@@ -21458,7 +22024,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>181</v>
+        <v>287</v>
       </c>
       <c r="C265">
         <v>927</v>
@@ -21535,7 +22101,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>182</v>
+        <v>288</v>
       </c>
       <c r="C266">
         <v>658</v>
@@ -21612,7 +22178,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>183</v>
+        <v>289</v>
       </c>
       <c r="C267">
         <v>1018</v>
@@ -21689,7 +22255,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>184</v>
+        <v>290</v>
       </c>
       <c r="C268">
         <v>1004</v>
@@ -21766,7 +22332,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>185</v>
+        <v>291</v>
       </c>
       <c r="C269">
         <v>1023</v>
@@ -21843,7 +22409,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="C270">
         <v>928</v>
@@ -21920,7 +22486,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>187</v>
+        <v>293</v>
       </c>
       <c r="C271">
         <v>1110</v>
@@ -21997,7 +22563,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>188</v>
+        <v>294</v>
       </c>
       <c r="C272">
         <v>1092</v>
@@ -22074,7 +22640,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>189</v>
+        <v>295</v>
       </c>
       <c r="C273">
         <v>1137</v>
@@ -22151,7 +22717,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>190</v>
+        <v>296</v>
       </c>
       <c r="C274">
         <v>1214</v>
@@ -22228,7 +22794,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>191</v>
+        <v>297</v>
       </c>
       <c r="C275">
         <v>1091</v>
@@ -22305,7 +22871,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>192</v>
+        <v>298</v>
       </c>
       <c r="C276">
         <v>444</v>
@@ -22382,7 +22948,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>193</v>
+        <v>299</v>
       </c>
       <c r="C277">
         <v>1017</v>
@@ -22459,7 +23025,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="C278">
         <v>1073</v>
@@ -22536,7 +23102,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>195</v>
+        <v>301</v>
       </c>
       <c r="C279">
         <v>1181</v>
@@ -22613,7 +23179,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>196</v>
+        <v>302</v>
       </c>
       <c r="C280">
         <v>1094</v>
@@ -22690,7 +23256,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>197</v>
+        <v>303</v>
       </c>
       <c r="C281">
         <v>996</v>
@@ -22767,7 +23333,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>198</v>
+        <v>304</v>
       </c>
       <c r="C282">
         <v>1116</v>
@@ -22844,7 +23410,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>199</v>
+        <v>305</v>
       </c>
       <c r="C283">
         <v>1073</v>
@@ -22921,7 +23487,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>200</v>
+        <v>306</v>
       </c>
       <c r="C284">
         <v>1042</v>
@@ -22998,7 +23564,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>201</v>
+        <v>307</v>
       </c>
       <c r="C285">
         <v>1071</v>
@@ -23075,7 +23641,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="C286">
         <v>1070</v>
@@ -23152,7 +23718,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="C287">
         <v>963</v>
@@ -23229,7 +23795,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="C288">
         <v>952</v>
@@ -23306,7 +23872,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>205</v>
+        <v>311</v>
       </c>
       <c r="C289">
         <v>915</v>
@@ -23383,7 +23949,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>206</v>
+        <v>312</v>
       </c>
       <c r="C290">
         <v>905</v>
@@ -23460,7 +24026,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>23</v>
+        <v>313</v>
       </c>
       <c r="C291">
         <v>959</v>
@@ -23537,7 +24103,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>24</v>
+        <v>314</v>
       </c>
       <c r="C292">
         <v>935</v>
@@ -23614,7 +24180,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>52</v>
+        <v>315</v>
       </c>
       <c r="C293">
         <v>974</v>
@@ -23691,7 +24257,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>207</v>
+        <v>316</v>
       </c>
       <c r="C294">
         <v>915</v>
@@ -23768,7 +24334,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>40</v>
+        <v>317</v>
       </c>
       <c r="C295">
         <v>817</v>
@@ -23845,7 +24411,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>41</v>
+        <v>318</v>
       </c>
       <c r="C296">
         <v>647</v>
@@ -23922,7 +24488,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>71</v>
+        <v>319</v>
       </c>
       <c r="C297">
         <v>1114</v>
@@ -23999,7 +24565,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>72</v>
+        <v>320</v>
       </c>
       <c r="C298">
         <v>1119</v>
@@ -24076,7 +24642,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>208</v>
+        <v>321</v>
       </c>
       <c r="C299">
         <v>877</v>
@@ -24153,7 +24719,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>209</v>
+        <v>322</v>
       </c>
       <c r="C300">
         <v>879</v>
@@ -24230,7 +24796,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>30</v>
+        <v>323</v>
       </c>
       <c r="C301">
         <v>1012</v>
@@ -24307,7 +24873,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>31</v>
+        <v>324</v>
       </c>
       <c r="C302">
         <v>1054</v>
@@ -24384,7 +24950,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>210</v>
+        <v>325</v>
       </c>
       <c r="C303">
         <v>914</v>
@@ -24461,7 +25027,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>211</v>
+        <v>326</v>
       </c>
       <c r="C304">
         <v>857</v>
@@ -24538,7 +25104,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>212</v>
+        <v>327</v>
       </c>
       <c r="C305">
         <v>1142</v>
@@ -24615,7 +25181,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>213</v>
+        <v>328</v>
       </c>
       <c r="C306">
         <v>703</v>
@@ -24692,7 +25258,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>214</v>
+        <v>329</v>
       </c>
       <c r="C307">
         <v>863</v>
@@ -24769,7 +25335,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>215</v>
+        <v>330</v>
       </c>
       <c r="C308">
         <v>745</v>
@@ -24846,7 +25412,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>216</v>
+        <v>331</v>
       </c>
       <c r="C309">
         <v>964</v>
@@ -24923,7 +25489,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>217</v>
+        <v>332</v>
       </c>
       <c r="C310">
         <v>1105</v>
@@ -25000,7 +25566,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>218</v>
+        <v>333</v>
       </c>
       <c r="C311">
         <v>978</v>
@@ -25077,7 +25643,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>219</v>
+        <v>334</v>
       </c>
       <c r="C312">
         <v>622</v>
@@ -25154,7 +25720,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>220</v>
+        <v>335</v>
       </c>
       <c r="C313">
         <v>643</v>
@@ -25231,7 +25797,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>221</v>
+        <v>336</v>
       </c>
       <c r="C314">
         <v>632</v>
@@ -25308,7 +25874,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>222</v>
+        <v>337</v>
       </c>
       <c r="C315">
         <v>1255</v>
@@ -25385,7 +25951,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>223</v>
+        <v>338</v>
       </c>
       <c r="C316">
         <v>697</v>
@@ -25462,7 +26028,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>224</v>
+        <v>339</v>
       </c>
       <c r="C317">
         <v>701</v>
@@ -25539,7 +26105,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>225</v>
+        <v>340</v>
       </c>
       <c r="C318">
         <v>662</v>
@@ -25616,7 +26182,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>226</v>
+        <v>341</v>
       </c>
       <c r="C319">
         <v>724</v>
@@ -25693,7 +26259,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>227</v>
+        <v>342</v>
       </c>
       <c r="C320">
         <v>942</v>
@@ -25770,7 +26336,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>228</v>
+        <v>343</v>
       </c>
       <c r="C321">
         <v>884</v>
@@ -25847,7 +26413,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>123</v>
+        <v>344</v>
       </c>
       <c r="C322">
         <v>978</v>
@@ -25924,7 +26490,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>229</v>
+        <v>345</v>
       </c>
       <c r="C323">
         <v>579</v>
@@ -26001,7 +26567,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>230</v>
+        <v>346</v>
       </c>
       <c r="C324">
         <v>1095</v>
@@ -26078,7 +26644,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>231</v>
+        <v>347</v>
       </c>
       <c r="C325">
         <v>840</v>
@@ -26155,7 +26721,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>232</v>
+        <v>348</v>
       </c>
       <c r="C326">
         <v>1079</v>
@@ -26232,7 +26798,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>233</v>
+        <v>349</v>
       </c>
       <c r="C327">
         <v>904</v>
@@ -26309,7 +26875,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>234</v>
+        <v>350</v>
       </c>
       <c r="C328">
         <v>827</v>
@@ -26386,7 +26952,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>235</v>
+        <v>351</v>
       </c>
       <c r="C329">
         <v>937</v>
@@ -26463,7 +27029,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>10</v>
+        <v>352</v>
       </c>
       <c r="C330">
         <v>649</v>
@@ -26540,7 +27106,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>11</v>
+        <v>353</v>
       </c>
       <c r="C331">
         <v>712</v>
@@ -26617,7 +27183,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>33</v>
+        <v>354</v>
       </c>
       <c r="C332">
         <v>809</v>
@@ -26694,7 +27260,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>34</v>
+        <v>355</v>
       </c>
       <c r="C333">
         <v>608</v>
@@ -26771,7 +27337,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>63</v>
+        <v>356</v>
       </c>
       <c r="C334">
         <v>526</v>
@@ -26848,7 +27414,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>51</v>
+        <v>357</v>
       </c>
       <c r="C335">
         <v>618</v>
@@ -26925,7 +27491,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>63</v>
+        <v>358</v>
       </c>
       <c r="C336">
         <v>898</v>
@@ -27002,7 +27568,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>51</v>
+        <v>359</v>
       </c>
       <c r="C337">
         <v>1005</v>
@@ -27079,7 +27645,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>21</v>
+        <v>360</v>
       </c>
       <c r="C338">
         <v>954</v>
@@ -27156,7 +27722,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>22</v>
+        <v>361</v>
       </c>
       <c r="C339">
         <v>646</v>
@@ -27233,7 +27799,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>5</v>
+        <v>362</v>
       </c>
       <c r="C340">
         <v>755</v>
@@ -27310,7 +27876,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>85</v>
+        <v>363</v>
       </c>
       <c r="C341">
         <v>769</v>
@@ -27387,7 +27953,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>128</v>
+        <v>364</v>
       </c>
       <c r="C342">
         <v>1035</v>
@@ -27464,7 +28030,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>16</v>
+        <v>365</v>
       </c>
       <c r="C343">
         <v>1183</v>
@@ -27541,7 +28107,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>17</v>
+        <v>366</v>
       </c>
       <c r="C344">
         <v>689</v>
@@ -27618,7 +28184,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>100</v>
+        <v>367</v>
       </c>
       <c r="C345">
         <v>934</v>
@@ -27695,7 +28261,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>236</v>
+        <v>368</v>
       </c>
       <c r="C346">
         <v>733</v>
@@ -27772,7 +28338,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>237</v>
+        <v>369</v>
       </c>
       <c r="C347">
         <v>818</v>
@@ -27849,7 +28415,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>23</v>
+        <v>370</v>
       </c>
       <c r="C348">
         <v>1096</v>
@@ -27926,7 +28492,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>24</v>
+        <v>371</v>
       </c>
       <c r="C349">
         <v>1046</v>
@@ -28003,7 +28569,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>238</v>
+        <v>372</v>
       </c>
       <c r="C350">
         <v>727</v>
@@ -28080,7 +28646,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>239</v>
+        <v>373</v>
       </c>
       <c r="C351">
         <v>618</v>
@@ -28157,7 +28723,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>240</v>
+        <v>374</v>
       </c>
       <c r="C352">
         <v>1017</v>
@@ -28234,7 +28800,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>241</v>
+        <v>375</v>
       </c>
       <c r="C353">
         <v>840</v>
@@ -28311,7 +28877,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>242</v>
+        <v>376</v>
       </c>
       <c r="C354">
         <v>644</v>
@@ -28388,7 +28954,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>243</v>
+        <v>377</v>
       </c>
       <c r="C355">
         <v>824</v>
@@ -28465,7 +29031,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>244</v>
+        <v>378</v>
       </c>
       <c r="C356">
         <v>884</v>
@@ -28542,7 +29108,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>245</v>
+        <v>379</v>
       </c>
       <c r="C357">
         <v>944</v>
@@ -28619,7 +29185,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>100</v>
+        <v>380</v>
       </c>
       <c r="C358">
         <v>765</v>
@@ -28696,7 +29262,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>3</v>
+        <v>381</v>
       </c>
       <c r="C359">
         <v>602</v>
@@ -28773,7 +29339,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>246</v>
+        <v>382</v>
       </c>
       <c r="C360">
         <v>1005</v>
@@ -28850,7 +29416,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>247</v>
+        <v>383</v>
       </c>
       <c r="C361">
         <v>778</v>
@@ -28927,7 +29493,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>248</v>
+        <v>384</v>
       </c>
       <c r="C362">
         <v>917</v>
@@ -29004,7 +29570,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>249</v>
+        <v>385</v>
       </c>
       <c r="C363">
         <v>1056</v>
@@ -29081,7 +29647,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>210</v>
+        <v>386</v>
       </c>
       <c r="C364">
         <v>663</v>
@@ -29158,7 +29724,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>250</v>
+        <v>387</v>
       </c>
       <c r="C365">
         <v>959</v>
@@ -29235,7 +29801,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>40</v>
+        <v>388</v>
       </c>
       <c r="C366">
         <v>687</v>
@@ -29312,7 +29878,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>41</v>
+        <v>389</v>
       </c>
       <c r="C367">
         <v>778</v>
@@ -29389,7 +29955,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>66</v>
+        <v>390</v>
       </c>
       <c r="C368">
         <v>1149</v>
@@ -29466,7 +30032,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>251</v>
+        <v>391</v>
       </c>
       <c r="C369">
         <v>889</v>
@@ -29543,7 +30109,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>252</v>
+        <v>392</v>
       </c>
       <c r="C370">
         <v>1129</v>
@@ -29620,7 +30186,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>253</v>
+        <v>393</v>
       </c>
       <c r="C371">
         <v>892</v>
@@ -29697,7 +30263,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>254</v>
+        <v>394</v>
       </c>
       <c r="C372">
         <v>710</v>
@@ -29774,7 +30340,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>23</v>
+        <v>395</v>
       </c>
       <c r="C373">
         <v>733</v>
@@ -29851,7 +30417,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>24</v>
+        <v>396</v>
       </c>
       <c r="C374">
         <v>748</v>
@@ -29928,7 +30494,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>100</v>
+        <v>397</v>
       </c>
       <c r="C375">
         <v>835</v>
@@ -30005,7 +30571,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>68</v>
+        <v>398</v>
       </c>
       <c r="C376">
         <v>968</v>
@@ -30082,7 +30648,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>40</v>
+        <v>399</v>
       </c>
       <c r="C377">
         <v>618</v>
@@ -30159,7 +30725,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>41</v>
+        <v>400</v>
       </c>
       <c r="C378">
         <v>600</v>
@@ -30236,7 +30802,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>23</v>
+        <v>401</v>
       </c>
       <c r="C379">
         <v>779</v>
@@ -30313,7 +30879,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>24</v>
+        <v>402</v>
       </c>
       <c r="C380">
         <v>469</v>
@@ -30390,7 +30956,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>3</v>
+        <v>403</v>
       </c>
       <c r="C381">
         <v>474</v>
@@ -30467,7 +31033,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>255</v>
+        <v>404</v>
       </c>
       <c r="C382">
         <v>839</v>
@@ -30544,7 +31110,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>5</v>
+        <v>405</v>
       </c>
       <c r="C383">
         <v>500</v>
@@ -30621,7 +31187,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>256</v>
+        <v>406</v>
       </c>
       <c r="C384">
         <v>958</v>
@@ -30698,7 +31264,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>257</v>
+        <v>407</v>
       </c>
       <c r="C385">
         <v>771</v>
@@ -30775,7 +31341,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>258</v>
+        <v>408</v>
       </c>
       <c r="C386">
         <v>829</v>
@@ -30852,7 +31418,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>259</v>
+        <v>409</v>
       </c>
       <c r="C387">
         <v>871</v>
@@ -30929,7 +31495,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>78</v>
+        <v>410</v>
       </c>
       <c r="C388">
         <v>648</v>
@@ -31006,7 +31572,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>4</v>
+        <v>411</v>
       </c>
       <c r="C389">
         <v>687</v>
@@ -31083,7 +31649,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>40</v>
+        <v>412</v>
       </c>
       <c r="C390">
         <v>493</v>
@@ -31160,7 +31726,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>41</v>
+        <v>413</v>
       </c>
       <c r="C391">
         <v>1001</v>
@@ -31237,7 +31803,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>40</v>
+        <v>414</v>
       </c>
       <c r="C392">
         <v>1004</v>
@@ -31314,7 +31880,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>41</v>
+        <v>415</v>
       </c>
       <c r="C393">
         <v>737</v>
